--- a/artfynd/A 63880-2021 artfynd.xlsx
+++ b/artfynd/A 63880-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63880-2021 artfynd.xlsx
+++ b/artfynd/A 63880-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89612638</v>
+        <v>89612639</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96446</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1079</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Aspfjädermossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Neckera pennata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>382216.8698436455</v>
+        <v>382133</v>
       </c>
       <c r="R2" t="n">
-        <v>6628074.767166075</v>
+        <v>6628111</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-12</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På död trol. sälg</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +775,7 @@
         <v>89612635</v>
       </c>
       <c r="B3" t="n">
-        <v>89403</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -841,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>382140.1206613075</v>
+        <v>382140</v>
       </c>
       <c r="R3" t="n">
-        <v>6628122.048549506</v>
+        <v>6628122</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,19 +849,9 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-11-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -913,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89612639</v>
+        <v>89612627</v>
       </c>
       <c r="B4" t="n">
-        <v>93148</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1079</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Aspfjädermossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera pennata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -953,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>382133.2139433254</v>
+        <v>382279</v>
       </c>
       <c r="R4" t="n">
-        <v>6628111.180375773</v>
+        <v>6627721</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,19 +946,14 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På asphögstubbe.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,15 +980,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89612627</v>
+        <v>89612637</v>
       </c>
       <c r="B5" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1065,10 +1015,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>382278.8805884712</v>
+        <v>382117</v>
       </c>
       <c r="R5" t="n">
-        <v>6627721.028534506</v>
+        <v>6627986</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,24 +1048,14 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>På asphögstubbe.</t>
+          <t>På asp.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,15 +1082,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>89612637</v>
+        <v>89612638</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1182,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>382117.1401440559</v>
+        <v>382217</v>
       </c>
       <c r="R6" t="n">
-        <v>6627986.203599212</v>
+        <v>6628075</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,24 +1150,14 @@
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2020-11-12</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>På asp.</t>
+          <t>På död trol. sälg</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1256,6 +1181,108 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>89612626</v>
+      </c>
+      <c r="B7" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Åmotsnäs, S om Norra Baksjön, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>382335</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6627655</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Arvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Brunskog</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2020-11-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2020-11-12</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt på gammal asp.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anders Boström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
